--- a/4_outputs/final/Table14.xlsx
+++ b/4_outputs/final/Table14.xlsx
@@ -417,356 +417,874 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>H1a</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>H1b</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>H1c</t>
-        </is>
-      </c>
+          <t>MPNet</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>H1d</t>
-        </is>
-      </c>
+          <t>MiniLM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SciBERT</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr"/>
+      <c r="J1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>It.</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cov. gap</t>
+          <t>acc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dominance</t>
+          <t>gap</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Research cov.\</t>
+          <t>p vs raw</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Policy cov.\</t>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>p vs raw</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>p vs raw</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sliced Wasserstein</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>+0.554^*</t>
+          <t>0.978</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+0.061</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+0.539^*</t>
+          <t>0.995</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+0.397</t>
+          <t>0.965</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.312</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.988</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.973</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.877</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Linear MMD</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>+0.603^*</t>
+          <t>0.938</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+0.022</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.466^</t>
+          <t>0.985</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.439^</t>
+          <t>0.913</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.285</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.976</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.792</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy distance</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>+0.537^*</t>
+          <t>0.895</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.074</t>
+          <t>0.290</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+0.532^*</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+0.384</t>
+          <t>0.852</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.951</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.755</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.748</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Squared RBF MMD</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+0.473^</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.113</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+0.551^*</t>
+          <t>0.980</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+0.296</t>
+          <t>0.796</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.922</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.691</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.757</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Exact EMD</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+0.304</t>
+          <t>0.831</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+0.147</t>
+          <t>0.279</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.167</t>
+          <t>0.973</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+0.217</t>
+          <t>0.763</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.234</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.882</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.738</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chamfer</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+0.103</t>
+          <t>0.747</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.115</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.350</t>
+          <t>0.708</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>0.633</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.188</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.532</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.581</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Modified Hausdorff</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>+0.159</t>
+          <t>0.685</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+0.152</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+0.127</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+0.066</t>
+          <t>0.584</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.173</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.392</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.539</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.608</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gaussian-2-Wasserstein</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.240</t>
+          <t>0.195</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+0.262</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.042</t>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.167</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.382</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.582</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.588</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sinkhorn</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.199</t>
+          <t>0.558</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.397</t>
+          <t>0.188</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.176</t>
+          <t>0.390</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.505^*</t>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.162</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.336</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.515</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C2ST AUC</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+0.270</t>
+          <t>0.535</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.275</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+0.375</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.139</t>
+          <t>0.498</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.161</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.328</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.596</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.463</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grassmann</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.186</t>
+          <t>0.523</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.034</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+0.012</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.228</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.581</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.034</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.485</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.512</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.187</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.338</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.562</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.036</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.483</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.498</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.187</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.338</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.552</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.038</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.491</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.471</t>
         </is>
       </c>
     </row>
